--- a/etf_holdings/2026-09-09_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-09-09_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL7"/>
+  <dimension ref="A1:BB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,200 +539,150 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>00403A_異動類型</t>
+          <t>00985A_異動類型</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>00403A_調整方向</t>
+          <t>00985A_調整方向</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>00403A_股票名稱_昨日</t>
+          <t>00985A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>00403A_股票名稱_今日</t>
+          <t>00985A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>00403A_權重_昨日</t>
+          <t>00985A_權重_昨日</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>00403A_權重_今日</t>
+          <t>00985A_權重_今日</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>00403A_權重變化</t>
+          <t>00985A_權重變化</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>00403A_股數_昨日</t>
+          <t>00985A_股數_昨日</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>00403A_股數_今日</t>
+          <t>00985A_股數_今日</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>00403A_股數變化</t>
+          <t>00985A_股數變化</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>00985A_異動類型</t>
+          <t>00405A_異動類型</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>00985A_調整方向</t>
+          <t>00405A_調整方向</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>00985A_股票名稱_昨日</t>
+          <t>00405A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>00985A_股票名稱_今日</t>
+          <t>00405A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>00985A_權重_昨日</t>
+          <t>00405A_權重_昨日</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>00985A_權重_今日</t>
+          <t>00405A_權重_今日</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>00985A_權重變化</t>
+          <t>00405A_權重變化</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>00985A_股數_昨日</t>
+          <t>00405A_股數_昨日</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>00985A_股數_今日</t>
+          <t>00405A_股數_今日</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>00985A_股數變化</t>
+          <t>00405A_股數變化</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>00405A_異動類型</t>
+          <t>00407A_異動類型</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>00405A_調整方向</t>
+          <t>00407A_調整方向</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>00405A_股票名稱_昨日</t>
+          <t>00407A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>00405A_股票名稱_今日</t>
+          <t>00407A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>00405A_權重_昨日</t>
+          <t>00407A_權重_昨日</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>00405A_權重_今日</t>
+          <t>00407A_權重_今日</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>00405A_權重變化</t>
+          <t>00407A_權重變化</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>00405A_股數_昨日</t>
+          <t>00407A_股數_昨日</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>00405A_股數_今日</t>
+          <t>00407A_股數_今日</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
-        <is>
-          <t>00405A_股數變化</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>00407A_異動類型</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>00407A_調整方向</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>00407A_股票名稱_昨日</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>00407A_股票名稱_今日</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>00407A_權重_昨日</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>00407A_權重_今日</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>00407A_權重變化</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>00407A_股數_昨日</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>00407A_股數_今日</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
         <is>
           <t>00407A_股數變化</t>
         </is>
@@ -869,58 +819,48 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>3.92%</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>-0.84%</t>
         </is>
       </c>
-      <c r="BJ2" t="n">
+      <c r="AZ2" t="n">
         <v>491644</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BA2" t="n">
         <v>421644</v>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>-70,000</t>
         </is>
@@ -929,12 +869,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -942,19 +882,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00403A,00985A</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>00985A,00991A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>智邦科技</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>智邦科技</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3.56%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3.42%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-0.14%</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -977,86 +953,50 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>15.86%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>15.59%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>10100000</v>
+        <v>97000</v>
       </c>
       <c r="AG3" t="n">
-        <v>10000000</v>
+        <v>80000</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-100,000</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>台灣積體電路製造</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>台灣積體電路製造</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>13.65%</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>14.98%</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>+1.33%</t>
-        </is>
-      </c>
-      <c r="AP3" t="n">
-        <v>588000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>637000</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>49,000</t>
-        </is>
-      </c>
+          <t>-17,000</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
@@ -1067,26 +1007,16 @@
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>欣興電子</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1094,55 +1024,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00985A,00991A</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>智邦科技</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>智邦科技</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3.56%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>3.42%</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-0.14%</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>1450000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-100,000</t>
-        </is>
-      </c>
+          <t>00405A,00985A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
@@ -1153,16 +1047,52 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>欣興電子</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>欣興電子</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>-0.46%</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>252000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>198000</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-54,000</t>
+        </is>
+      </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>持續持有</t>
@@ -1170,43 +1100,43 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>5.45%</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>6.20%</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.75%</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>97000</v>
+        <v>1570000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>80000</v>
+        <v>1720000</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-17,000</t>
+          <t>150,000</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
@@ -1219,26 +1149,16 @@
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>欣興電子</t>
+          <t>弘塑</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1246,7 +1166,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00405A,00985A</t>
+          <t>00405A,00407A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1291,106 +1211,78 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>欣興電子</t>
+          <t>弘塑</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>欣興電子</t>
+          <t>弘塑</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>252000</v>
+        <v>152000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>198000</v>
+        <v>132000</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-54,000</t>
+          <t>-20,000</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>5.45%</t>
-        </is>
-      </c>
+          <t>弘塑</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>6.20%</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>+0.75%</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1570000</v>
-      </c>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>1720000</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>150,000</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
+        <v>91000</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>弘塑</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1398,7 +1290,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00405A,00407A</t>
+          <t>00407A,00985A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -1421,16 +1313,52 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0.79%</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>77000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>-17,000</t>
+        </is>
+      </c>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
@@ -1448,221 +1376,41 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>弘塑</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>弘塑</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>152000</v>
+        <v>250000</v>
       </c>
       <c r="BA6" t="n">
-        <v>132000</v>
+        <v>290000</v>
       </c>
       <c r="BB6" t="inlineStr">
-        <is>
-          <t>-20,000</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>弘塑</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>0.95%</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="n">
-        <v>91000</v>
-      </c>
-      <c r="BL6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>00407A,00985A</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>1.00%</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>0.79%</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>-0.21%</t>
-        </is>
-      </c>
-      <c r="AP7" t="n">
-        <v>77000</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>60000</v>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-17,000</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>1.33%</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>1.60%</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>+0.27%</t>
-        </is>
-      </c>
-      <c r="BJ7" t="n">
-        <v>250000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>290000</v>
-      </c>
-      <c r="BL7" t="inlineStr">
         <is>
           <t>40,000</t>
         </is>

--- a/etf_holdings/2026-09-09_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-09-09_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB6"/>
+  <dimension ref="A1:BL7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,150 +539,200 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>00403A_異動類型</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>00403A_調整方向</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>00403A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>00403A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>00403A_權重變化</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>00403A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>00403A_股數_今日</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>00403A_股數變化</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
           <t>00985A_異動類型</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>00985A_調整方向</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>00985A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>00985A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>00985A_權重_昨日</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>00985A_權重_今日</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>00985A_權重變化</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>00985A_股數_昨日</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>00985A_股數_今日</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>00985A_股數變化</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>00405A_異動類型</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>00405A_調整方向</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>00405A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>00405A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>00405A_權重_昨日</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>00405A_權重_今日</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>00405A_權重變化</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>00405A_股數_昨日</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>00405A_股數_今日</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>00405A_股數變化</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>00407A_異動類型</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>00407A_調整方向</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>00407A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>00407A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>00407A_權重_昨日</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>00407A_權重_今日</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>00407A_權重變化</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>00407A_股數_昨日</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>00407A_股數_今日</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>00407A_股數變化</t>
         </is>
@@ -819,48 +869,58 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr">
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>3.92%</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>-0.84%</t>
         </is>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BJ2" t="n">
         <v>491644</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BK2" t="n">
         <v>421644</v>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>-70,000</t>
         </is>
@@ -869,12 +929,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -882,55 +942,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00985A,00991A</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>智邦科技</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>智邦科技</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3.56%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>3.42%</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-0.14%</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>1450000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>-100,000</t>
-        </is>
-      </c>
+          <t>00403A,00985A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -953,50 +977,86 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>15.86%</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>15.59%</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>97000</v>
+        <v>10100000</v>
       </c>
       <c r="AG3" t="n">
-        <v>80000</v>
+        <v>10000000</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-17,000</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>台灣積體電路製造</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>台灣積體電路製造</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>13.65%</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>14.98%</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>+1.33%</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>588000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>637000</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>49,000</t>
+        </is>
+      </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
@@ -1007,16 +1067,26 @@
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>欣興電子</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1024,19 +1094,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00405A,00985A</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>00985A,00991A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>智邦科技</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>智邦科技</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3.56%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3.42%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-0.14%</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
@@ -1047,96 +1153,60 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>欣興電子</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>欣興電子</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2.26%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>1.80%</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>-0.46%</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>252000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>198000</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-54,000</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>5.45%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>6.20%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>1570000</v>
+        <v>97000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1720000</v>
+        <v>80000</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>150,000</t>
+          <t>-17,000</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
@@ -1149,16 +1219,26 @@
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>弘塑</t>
+          <t>欣興電子</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1166,7 +1246,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00405A,00407A</t>
+          <t>00405A,00985A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1211,78 +1291,106 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>弘塑</t>
+          <t>欣興電子</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>弘塑</t>
+          <t>欣興電子</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>152000</v>
+        <v>252000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>132000</v>
+        <v>198000</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-20,000</t>
+          <t>-54,000</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr"/>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>弘塑</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr"/>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>5.45%</t>
+        </is>
+      </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.95%</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
+          <t>6.20%</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>+0.75%</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1570000</v>
+      </c>
       <c r="BA5" t="n">
-        <v>91000</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
+        <v>1720000</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>150,000</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>弘塑</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1290,7 +1398,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00407A,00985A</t>
+          <t>00405A,00407A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -1313,52 +1421,16 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1.00%</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>0.79%</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>-0.21%</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>77000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>60000</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>-17,000</t>
-        </is>
-      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
@@ -1376,41 +1448,221 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>弘塑</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>弘塑</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>152000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>132000</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>弘塑</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="n">
+        <v>91000</v>
+      </c>
+      <c r="BL6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00407A,00985A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.79%</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="AP7" t="n">
+        <v>77000</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>60000</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-17,000</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AU6" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>
       </c>
-      <c r="AV6" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>1.33%</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>1.60%</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>+0.27%</t>
         </is>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BJ7" t="n">
         <v>250000</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BK7" t="n">
         <v>290000</v>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>40,000</t>
         </is>
